--- a/Ozrit HR data/ozrit/Admin/Maintenance, internet,vehicle/Maintenance.xlsx
+++ b/Ozrit HR data/ozrit/Admin/Maintenance, internet,vehicle/Maintenance.xlsx
@@ -1,17 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rani\Downloads\ozrit\Ozrit HR data\ozrit\Admin\Maintenance, internet,vehicle\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D3EAA44-F48D-478C-B471-C28211DCDF03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Paid " sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="119">
   <si>
     <t xml:space="preserve">maintenance </t>
   </si>
@@ -125,15 +136,9 @@
     <t>SVC147331</t>
   </si>
   <si>
-    <t>B3(135-137)</t>
-  </si>
-  <si>
     <t>Pradeep</t>
   </si>
   <si>
-    <t xml:space="preserve">B3135 </t>
-  </si>
-  <si>
     <t xml:space="preserve">March </t>
   </si>
   <si>
@@ -146,9 +151,6 @@
     <t>Manikanta</t>
   </si>
   <si>
-    <t>B3 136</t>
-  </si>
-  <si>
     <t xml:space="preserve">april </t>
   </si>
   <si>
@@ -158,44 +160,375 @@
     <t>ravindhra</t>
   </si>
   <si>
-    <t>B3 137</t>
-  </si>
-  <si>
     <t>TWC/052025/007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">June </t>
+  </si>
+  <si>
+    <t>July</t>
+  </si>
+  <si>
+    <t xml:space="preserve">August </t>
+  </si>
+  <si>
+    <t>M/U/082025/011</t>
+  </si>
+  <si>
+    <t>M/U/072025/011</t>
+  </si>
+  <si>
+    <t>September</t>
+  </si>
+  <si>
+    <t>Paid</t>
+  </si>
+  <si>
+    <t>SVC148308</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>TWC/082025/006</t>
+  </si>
+  <si>
+    <t>TWC/062025/006</t>
+  </si>
+  <si>
+    <t>027</t>
+  </si>
+  <si>
+    <t>028</t>
+  </si>
+  <si>
+    <t>030</t>
+  </si>
+  <si>
+    <t>038</t>
+  </si>
+  <si>
+    <t>039</t>
+  </si>
+  <si>
+    <t>029</t>
+  </si>
+  <si>
+    <t>B3</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>Mohan</t>
+  </si>
+  <si>
+    <t>Kiran</t>
+  </si>
+  <si>
+    <t>Raghu</t>
+  </si>
+  <si>
+    <t>Chetan</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>Manish                                     </t>
+  </si>
+  <si>
+    <t>Sayeed Anzer                      </t>
+  </si>
+  <si>
+    <t>Chary                                     </t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>Yuva kiran</t>
+  </si>
+  <si>
+    <t>TWS/092025/006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Months </t>
+  </si>
+  <si>
+    <t>Maintenance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bike parking </t>
+  </si>
+  <si>
+    <t>feb</t>
+  </si>
+  <si>
+    <t>mar</t>
+  </si>
+  <si>
+    <t>apr</t>
+  </si>
+  <si>
+    <t>may</t>
+  </si>
+  <si>
+    <t>jun</t>
+  </si>
+  <si>
+    <t>jul</t>
+  </si>
+  <si>
+    <t>aug</t>
+  </si>
+  <si>
+    <t xml:space="preserve">payments date </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slno </t>
+  </si>
+  <si>
+    <t xml:space="preserve">bharath sir </t>
+  </si>
+  <si>
+    <t>27.03.2025</t>
+  </si>
+  <si>
+    <t>6.03.2035</t>
+  </si>
+  <si>
+    <t>3.04.2025</t>
+  </si>
+  <si>
+    <t>2,76,950</t>
+  </si>
+  <si>
+    <t>Paid by</t>
+  </si>
+  <si>
+    <t>29.06.2025</t>
+  </si>
+  <si>
+    <t>24.08.2025</t>
+  </si>
+  <si>
+    <t>04.09.2025</t>
+  </si>
+  <si>
+    <t>29.09.2025</t>
+  </si>
+  <si>
+    <t>3,47,836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sep </t>
+  </si>
+  <si>
+    <t xml:space="preserve">We paid </t>
+  </si>
+  <si>
+    <t>Grand total</t>
+  </si>
+  <si>
+    <t>Paid till now </t>
+  </si>
+  <si>
+    <t>Balance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">till August </t>
+  </si>
+  <si>
+    <t xml:space="preserve">till September </t>
+  </si>
+  <si>
+    <t>Total maintenancebill</t>
+  </si>
+  <si>
+    <t>Total bikes slot</t>
+  </si>
+  <si>
+    <t>left</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nani prasad </t>
+  </si>
+  <si>
+    <t>gopi</t>
+  </si>
+  <si>
+    <t>Hruthik</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF2C363A"/>
       <name val="Verdana"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF2C363A"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF2C363A"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF2C363A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF006A9D"/>
       <name val="Verdana"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF2C363A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -203,9 +536,21 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
-    <border/>
+  <borders count="11">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -219,42 +564,265 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
+  <cellXfs count="52">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="12" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="12" fontId="18" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -444,23 +1012,26 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:N43"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="3" max="3" width="12.88"/>
-    <col customWidth="1" min="6" max="6" width="17.75"/>
-    <col customWidth="1" min="11" max="11" width="15.75"/>
-    <col customWidth="1" min="13" max="13" width="15.38"/>
+    <col min="3" max="3" width="17.6328125" customWidth="1"/>
+    <col min="6" max="6" width="17.7265625" customWidth="1"/>
+    <col min="11" max="11" width="15.7265625" customWidth="1"/>
+    <col min="13" max="13" width="15.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -468,26 +1039,26 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="7" t="s">
         <v>7</v>
       </c>
       <c r="I2" s="2" t="s">
@@ -506,30 +1077,30 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="B3" s="2" t="s">
+    <row r="3" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="7">
+        <v>1</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="2">
-        <v>29344.0</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="D3" s="7">
+        <v>29344</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="7" t="s">
         <v>15</v>
       </c>
       <c r="I3" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>11</v>
@@ -538,30 +1109,30 @@
         <v>16</v>
       </c>
       <c r="L3" s="2">
-        <v>2283.0</v>
+        <v>2283</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="B4" s="2" t="s">
+    <row r="4" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="7">
+        <v>2</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="2">
-        <v>33599.0</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
+      <c r="D4" s="7">
+        <v>33599</v>
+      </c>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
       <c r="I4" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>20</v>
@@ -570,30 +1141,30 @@
         <v>21</v>
       </c>
       <c r="L4" s="2">
-        <v>5899.0</v>
+        <v>5899</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="B5" s="2" t="s">
+    <row r="5" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="7">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="2">
-        <v>37332.0</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
+      <c r="D5" s="7">
+        <v>37332</v>
+      </c>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
       <c r="I5" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -602,30 +1173,30 @@
         <v>25</v>
       </c>
       <c r="L5" s="2">
-        <v>5899.0</v>
+        <v>5899</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="B6" s="2" t="s">
+    <row r="6" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="7">
+        <v>4</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="2">
-        <v>45980.0</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
+      <c r="D6" s="7">
+        <v>45980</v>
+      </c>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
       <c r="I6" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>26</v>
@@ -634,30 +1205,30 @@
         <v>28</v>
       </c>
       <c r="L6" s="2">
-        <v>5899.0</v>
+        <v>5899</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1">
-      <c r="A7" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="B7" s="2" t="s">
+    <row r="7" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="7">
+        <v>5</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="1">
-        <v>48923.0</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
+      <c r="D7" s="7">
+        <v>48923</v>
+      </c>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
       <c r="I7" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>32</v>
@@ -666,7 +1237,7 @@
         <v>33</v>
       </c>
       <c r="L7" s="2">
-        <v>5899.0</v>
+        <v>5899</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>29</v>
@@ -675,16 +1246,24 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
+    <row r="8" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="8">
+        <v>6</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="8">
+        <v>33599</v>
+      </c>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
       <c r="I8" s="2">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>35</v>
@@ -693,67 +1272,104 @@
         <v>36</v>
       </c>
       <c r="L8" s="2">
-        <v>5899.0</v>
+        <v>5899</v>
       </c>
       <c r="M8" s="3"/>
     </row>
-    <row r="9">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
+    <row r="9" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="8">
+        <v>7</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="8">
+        <v>46881</v>
+      </c>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
       <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
+      <c r="J9" s="3" t="s">
+        <v>47</v>
+      </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
     </row>
-    <row r="10">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
+    <row r="10" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="8">
+        <v>8</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="8">
+        <v>43678</v>
+      </c>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
       <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
+      <c r="J10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K10" t="s">
+        <v>53</v>
+      </c>
+      <c r="L10" s="3">
+        <v>7079</v>
+      </c>
       <c r="M10" s="3"/>
     </row>
-    <row r="11">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
+    <row r="11" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="11">
+        <f>SUM(D3:D10)</f>
+        <v>319336</v>
+      </c>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
       <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
+      <c r="J11" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K11" t="s">
+        <v>19</v>
+      </c>
+      <c r="L11" s="3">
+        <v>7079</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -767,10 +1383,8 @@
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
     </row>
-    <row r="17">
-      <c r="B17" s="4" t="s">
-        <v>37</v>
-      </c>
+    <row r="17" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="B17" s="4"/>
       <c r="I17" s="2" t="s">
         <v>1</v>
       </c>
@@ -787,139 +1401,983 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="5" t="s">
+    <row r="18" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="B18" s="4"/>
+      <c r="I18" s="2">
+        <v>1</v>
+      </c>
+      <c r="J18" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="K18" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="L18" s="2">
+        <v>1800</v>
+      </c>
+      <c r="M18" s="2"/>
+    </row>
+    <row r="19" spans="1:13" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" s="27">
+        <v>135</v>
+      </c>
+      <c r="I19" s="2">
+        <v>2</v>
+      </c>
+      <c r="J19" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="K19" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="I18" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="J18" s="2" t="s">
+      <c r="L19" s="2">
+        <v>1800</v>
+      </c>
+      <c r="M19" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="K18" s="2" t="s">
+    </row>
+    <row r="20" spans="1:13" ht="15" x14ac:dyDescent="0.3">
+      <c r="A20" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="L18" s="2">
-        <v>1800.0</v>
-      </c>
-      <c r="M18" s="2" t="s">
+      <c r="B20" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="27">
+        <v>136</v>
+      </c>
+      <c r="E20" s="14"/>
+      <c r="I20" s="2">
+        <v>3</v>
+      </c>
+      <c r="J20" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="s">
+      <c r="K20" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="L20" s="2">
+        <v>1800</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="15" x14ac:dyDescent="0.3">
+      <c r="A21" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="I19" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="J19" s="2" t="s">
+      <c r="B21" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" s="27">
+        <v>137</v>
+      </c>
+      <c r="E21" s="15"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="I21" s="2">
+        <v>4</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K21" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="K19" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L19" s="2">
-        <v>1800.0</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="s">
+      <c r="L21" s="2">
+        <v>3300</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="26"/>
+      <c r="B22" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="I22" s="2">
+        <v>5</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="K22" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="L22" s="3">
+        <v>4200</v>
+      </c>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="1:13" ht="15.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="26"/>
+      <c r="B23" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="E23" s="17"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="I23" s="2">
+        <v>6</v>
+      </c>
+      <c r="J23" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="K23" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="L23" s="3">
+        <v>4800</v>
+      </c>
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="1:13" ht="15.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="E24" s="17"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="I24" s="2">
+        <v>7</v>
+      </c>
+      <c r="J24" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="I20" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="L20" s="2">
-        <v>3300.0</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22">
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23">
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24">
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
+      <c r="K24" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="L24" s="3">
+        <v>4800</v>
+      </c>
       <c r="M24" s="3"/>
     </row>
-    <row r="25">
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
+    <row r="25" spans="1:13" ht="15.5" x14ac:dyDescent="0.3">
+      <c r="A25" s="26"/>
+      <c r="B25" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="E25" s="17"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="I25" s="2">
+        <v>8</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="L25" s="29">
+        <v>6000</v>
+      </c>
       <c r="M25" s="3"/>
     </row>
-    <row r="26">
+    <row r="26" spans="1:13" ht="14" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="E26" s="20"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
       <c r="I26" s="3"/>
-      <c r="J26" s="2"/>
+      <c r="J26" s="3"/>
       <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
+      <c r="L26" s="3">
+        <f>SUM(L18:L25)</f>
+        <v>28500</v>
+      </c>
       <c r="M26" s="3"/>
     </row>
-    <row r="27">
+    <row r="27" spans="1:13" ht="14" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="E27" s="21"/>
+      <c r="F27" s="22"/>
       <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
+      <c r="J27" s="2"/>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
     </row>
-    <row r="28">
+    <row r="28" spans="1:13" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A28" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="E28" s="23"/>
+      <c r="F28" s="24"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
     </row>
-    <row r="29">
+    <row r="29" spans="1:13" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" s="27" t="s">
+        <v>71</v>
+      </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
     </row>
+    <row r="30" spans="1:13" ht="15.5" x14ac:dyDescent="0.25">
+      <c r="A30" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C30" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="19"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="17"/>
+    </row>
+    <row r="32" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C33" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C34" s="27" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C35" s="27" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C36" s="27" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="26"/>
+      <c r="B37" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C37" s="27"/>
+    </row>
+    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C38" s="16"/>
+    </row>
+    <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C39" s="16"/>
+    </row>
+    <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C40" s="16"/>
+    </row>
+    <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C41" s="16"/>
+    </row>
+    <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C42" s="16"/>
+    </row>
+    <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C43" s="16"/>
+    </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="10" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A70610D-E260-4CE5-B0C6-6AE481912F5A}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.1796875" customWidth="1"/>
+    <col min="3" max="3" width="15.81640625" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" customWidth="1"/>
+    <col min="5" max="5" width="12.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B2" s="7">
+        <v>29344</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" s="7">
+        <v>33599</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="7">
+        <v>37332</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="7">
+        <v>45980</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" s="7">
+        <v>48923</v>
+      </c>
+      <c r="C6" s="2">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" s="8">
+        <v>33599</v>
+      </c>
+      <c r="C7" s="3">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" s="8">
+        <v>46881</v>
+      </c>
+      <c r="C8" s="3">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="8">
+        <v>43678</v>
+      </c>
+      <c r="C9" s="3">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="13" x14ac:dyDescent="0.3">
+      <c r="B10" s="30">
+        <f>SUM(B2:B9)</f>
+        <v>319336</v>
+      </c>
+      <c r="C10" s="31">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="13" x14ac:dyDescent="0.3">
+      <c r="C11" s="30">
+        <f>SUM(C3:C10)</f>
+        <v>28500</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C6B09E9-9C1E-4FC7-AE41-822C24388E8A}">
+  <dimension ref="A1:J25"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="20.90625" style="39" customWidth="1"/>
+    <col min="3" max="3" width="14.81640625" style="39" customWidth="1"/>
+    <col min="4" max="4" width="18.90625" style="39" customWidth="1"/>
+    <col min="7" max="7" width="16.26953125" customWidth="1"/>
+    <col min="8" max="8" width="22.54296875" customWidth="1"/>
+    <col min="9" max="9" width="10.36328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="30" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A1" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="36" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="F1" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="G1" s="36" t="s">
+        <v>83</v>
+      </c>
+      <c r="H1" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="I1" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="J1" s="32" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="9">
+        <v>1</v>
+      </c>
+      <c r="B2" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" s="40">
+        <v>29344</v>
+      </c>
+      <c r="D2" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="F2" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="G2" s="43">
+        <v>29344</v>
+      </c>
+      <c r="H2" s="38">
+        <v>0</v>
+      </c>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="B3" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" s="40">
+        <v>43238</v>
+      </c>
+      <c r="D3" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="F3" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3" s="43">
+        <v>33599</v>
+      </c>
+      <c r="H3" s="43">
+        <v>1800</v>
+      </c>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="B4" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="40">
+        <v>20000</v>
+      </c>
+      <c r="D4" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="F4" s="38" t="s">
+        <v>86</v>
+      </c>
+      <c r="G4" s="43">
+        <v>37332</v>
+      </c>
+      <c r="H4" s="43">
+        <v>1800</v>
+      </c>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="B5" s="37" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" s="40">
+        <v>29149</v>
+      </c>
+      <c r="D5" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="F5" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="G5" s="43">
+        <v>45980</v>
+      </c>
+      <c r="H5" s="43">
+        <v>1800</v>
+      </c>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="B6" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" s="40">
+        <v>30000</v>
+      </c>
+      <c r="D6" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="F6" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="G6" s="43">
+        <v>48923</v>
+      </c>
+      <c r="H6" s="43">
+        <v>3300</v>
+      </c>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="9">
+        <v>6</v>
+      </c>
+      <c r="B7" s="37" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" s="40">
+        <v>50000</v>
+      </c>
+      <c r="D7" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="F7" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="G7" s="43">
+        <v>33599</v>
+      </c>
+      <c r="H7" s="43">
+        <v>4200</v>
+      </c>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="9">
+        <v>7</v>
+      </c>
+      <c r="B8" s="37" t="s">
+        <v>104</v>
+      </c>
+      <c r="C8" s="40">
+        <v>75219</v>
+      </c>
+      <c r="D8" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="F8" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="G8" s="43">
+        <v>46881</v>
+      </c>
+      <c r="H8" s="43">
+        <v>4800</v>
+      </c>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+    </row>
+    <row r="9" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="9"/>
+      <c r="B9" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="41">
+        <f>SUM(C2:C8)</f>
+        <v>276950</v>
+      </c>
+      <c r="D9" s="38"/>
+      <c r="F9" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="G9" s="43">
+        <v>43678</v>
+      </c>
+      <c r="H9" s="43">
+        <v>4800</v>
+      </c>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="46"/>
+      <c r="D10" s="47"/>
+      <c r="F10" s="37" t="s">
+        <v>106</v>
+      </c>
+      <c r="G10" s="9"/>
+      <c r="H10" s="44">
+        <v>6000</v>
+      </c>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+    </row>
+    <row r="11" spans="1:10" ht="13" x14ac:dyDescent="0.3">
+      <c r="A11" s="48"/>
+      <c r="F11" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11" s="36">
+        <f>SUM(G2:G9)</f>
+        <v>319336</v>
+      </c>
+      <c r="H11" s="36">
+        <f>SUM(H3:H10)</f>
+        <v>28500</v>
+      </c>
+      <c r="I11" s="45">
+        <v>276950</v>
+      </c>
+      <c r="J11" s="51">
+        <v>70886</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="13" x14ac:dyDescent="0.3">
+      <c r="A12" s="48"/>
+      <c r="B12" s="32" t="s">
+        <v>113</v>
+      </c>
+      <c r="C12" s="35">
+        <v>319336</v>
+      </c>
+      <c r="D12" s="33" t="s">
+        <v>111</v>
+      </c>
+      <c r="F12" s="38"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+    </row>
+    <row r="13" spans="1:10" ht="13" x14ac:dyDescent="0.3">
+      <c r="A13" s="48"/>
+      <c r="B13" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="C13" s="35">
+        <v>28500</v>
+      </c>
+      <c r="D13" s="33" t="s">
+        <v>112</v>
+      </c>
+      <c r="F13" s="38"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="38"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+    </row>
+    <row r="14" spans="1:10" ht="13" x14ac:dyDescent="0.3">
+      <c r="A14" s="48"/>
+      <c r="B14" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="C14" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="D14" s="9"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="38"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+    </row>
+    <row r="15" spans="1:10" ht="13" x14ac:dyDescent="0.3">
+      <c r="A15" s="48"/>
+      <c r="B15" s="32" t="s">
+        <v>109</v>
+      </c>
+      <c r="C15" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="D15" s="9"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+    </row>
+    <row r="16" spans="1:10" ht="13" x14ac:dyDescent="0.3">
+      <c r="A16" s="48"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="9"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+    </row>
+    <row r="17" spans="1:10" ht="13" x14ac:dyDescent="0.3">
+      <c r="A17" s="48"/>
+      <c r="B17" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="C17" s="51">
+        <v>70886</v>
+      </c>
+      <c r="D17" s="9"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="48"/>
+      <c r="B18" s="49"/>
+      <c r="C18" s="50"/>
+      <c r="D18" s="49"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="48"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="49"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="48"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="49"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="38"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="48"/>
+      <c r="B21" s="49"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="49"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="48"/>
+      <c r="B22" s="49"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="49"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="38"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="48"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="49"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="38"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="48"/>
+      <c r="B24" s="49"/>
+      <c r="C24" s="49"/>
+      <c r="D24" s="49"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="38"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="48"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="49"/>
+      <c r="D25" s="49"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="38"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Ozrit HR data/ozrit/Admin/Maintenance, internet,vehicle/Maintenance.xlsx
+++ b/Ozrit HR data/ozrit/Admin/Maintenance, internet,vehicle/Maintenance.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rani\Downloads\ozrit\Ozrit HR data\ozrit\Admin\Maintenance, internet,vehicle\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D3EAA44-F48D-478C-B471-C28211DCDF03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE870634-74DE-4458-A93D-5BDF431772F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="130">
   <si>
     <t xml:space="preserve">maintenance </t>
   </si>
@@ -145,9 +145,6 @@
     <t>TWC/032025/006</t>
   </si>
   <si>
-    <t xml:space="preserve">not paid </t>
-  </si>
-  <si>
     <t>Manikanta</t>
   </si>
   <si>
@@ -380,6 +377,42 @@
   </si>
   <si>
     <t>Hruthik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">September </t>
+  </si>
+  <si>
+    <t xml:space="preserve">October </t>
+  </si>
+  <si>
+    <t>M/U/082025/012</t>
+  </si>
+  <si>
+    <t>M/U/082025/013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not paid </t>
+  </si>
+  <si>
+    <t>October</t>
+  </si>
+  <si>
+    <t xml:space="preserve">November </t>
+  </si>
+  <si>
+    <t>SVC149710</t>
+  </si>
+  <si>
+    <t>SVC149259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paid by vishwa </t>
+  </si>
+  <si>
+    <t>TWS/102025/006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not Paid </t>
   </si>
 </sst>
 </file>
@@ -523,7 +556,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -542,8 +575,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -693,11 +732,57 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -804,6 +889,14 @@
     <xf numFmtId="3" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1022,7 +1115,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:N43"/>
+  <dimension ref="A1:N45"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="17.6328125" customWidth="1"/>
@@ -1128,7 +1221,9 @@
       <c r="D4" s="7">
         <v>33599</v>
       </c>
-      <c r="E4" s="8"/>
+      <c r="E4" s="7" t="s">
+        <v>13</v>
+      </c>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="I4" s="2">
@@ -1143,7 +1238,7 @@
       <c r="L4" s="2">
         <v>5899</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" s="57" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1160,7 +1255,9 @@
       <c r="D5" s="7">
         <v>37332</v>
       </c>
-      <c r="E5" s="8"/>
+      <c r="E5" s="7" t="s">
+        <v>13</v>
+      </c>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
       <c r="I5" s="2">
@@ -1172,10 +1269,10 @@
       <c r="K5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L5" s="2">
+      <c r="L5" s="54">
         <v>5899</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="M5" s="7" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1192,7 +1289,9 @@
       <c r="D6" s="7">
         <v>45980</v>
       </c>
-      <c r="E6" s="8"/>
+      <c r="E6" s="7" t="s">
+        <v>13</v>
+      </c>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
       <c r="I6" s="2">
@@ -1204,10 +1303,10 @@
       <c r="K6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L6" s="54">
         <v>5899</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="M6" s="7" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1224,7 +1323,9 @@
       <c r="D7" s="7">
         <v>48923</v>
       </c>
-      <c r="E7" s="8"/>
+      <c r="E7" s="7" t="s">
+        <v>13</v>
+      </c>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
       <c r="I7" s="2">
@@ -1236,10 +1337,10 @@
       <c r="K7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="L7" s="2">
+      <c r="L7" s="54">
         <v>5899</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="M7" s="7" t="s">
         <v>29</v>
       </c>
       <c r="N7" s="1" t="s">
@@ -1251,7 +1352,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>19</v>
@@ -1259,7 +1360,9 @@
       <c r="D8" s="8">
         <v>33599</v>
       </c>
-      <c r="E8" s="8"/>
+      <c r="E8" s="7" t="s">
+        <v>13</v>
+      </c>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
       <c r="I8" s="2">
@@ -1271,515 +1374,610 @@
       <c r="K8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="L8" s="2">
+      <c r="L8" s="54">
         <v>5899</v>
       </c>
-      <c r="M8" s="3"/>
+      <c r="M8" s="8"/>
     </row>
     <row r="9" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
         <v>7</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D9" s="8">
         <v>46881</v>
       </c>
-      <c r="E9" s="8"/>
+      <c r="E9" s="52" t="s">
+        <v>122</v>
+      </c>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
-      <c r="I9" s="3"/>
+      <c r="I9" s="2">
+        <v>7</v>
+      </c>
       <c r="J9" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="8"/>
     </row>
     <row r="10" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <v>8</v>
       </c>
       <c r="B10" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>48</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>49</v>
       </c>
       <c r="D10" s="8">
         <v>43678</v>
       </c>
-      <c r="E10" s="8"/>
+      <c r="E10" s="52" t="s">
+        <v>122</v>
+      </c>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
-      <c r="I10" s="3"/>
+      <c r="I10" s="2">
+        <v>8</v>
+      </c>
       <c r="J10" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K10" t="s">
-        <v>53</v>
-      </c>
-      <c r="L10" s="3">
+        <v>52</v>
+      </c>
+      <c r="L10" s="55">
         <v>7079</v>
       </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="D11" s="11">
-        <f>SUM(D3:D10)</f>
-        <v>319336</v>
-      </c>
-      <c r="E11" s="8"/>
+      <c r="M10" s="8"/>
+    </row>
+    <row r="11" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="8">
+        <v>9</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="D11" s="8">
+        <v>45164</v>
+      </c>
+      <c r="E11" s="52" t="s">
+        <v>122</v>
+      </c>
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
-      <c r="I11" s="3"/>
+      <c r="I11" s="2">
+        <v>9</v>
+      </c>
       <c r="J11" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K11" t="s">
         <v>19</v>
       </c>
-      <c r="L11" s="3">
+      <c r="L11" s="55">
         <v>7079</v>
       </c>
-      <c r="M11" s="3" t="s">
-        <v>52</v>
+      <c r="M11" s="8" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="17" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="B17" s="4"/>
-      <c r="I17" s="2" t="s">
+      <c r="A12" s="8">
+        <v>10</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="D12" s="8">
+        <v>44878</v>
+      </c>
+      <c r="E12" s="52" t="s">
+        <v>122</v>
+      </c>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="I12" s="2">
+        <v>10</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="K12" t="s">
+        <v>126</v>
+      </c>
+      <c r="L12" s="55">
+        <v>7079</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="11">
+        <f>SUM(D3:D12)</f>
+        <v>409378</v>
+      </c>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="I13" s="3">
+        <v>11</v>
+      </c>
+      <c r="J13" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="K13" t="s">
+        <v>125</v>
+      </c>
+      <c r="L13" s="56">
+        <v>7079</v>
+      </c>
+      <c r="M13" s="9" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="8"/>
+    </row>
+    <row r="15" spans="1:14" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="8"/>
+    </row>
+    <row r="18" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E18">
+        <v>90042</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="B19" s="4"/>
+      <c r="E19">
+        <v>6000</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J17" s="2" t="s">
+      <c r="J19" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="K17" s="2" t="s">
+      <c r="K19" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="L17" s="2" t="s">
+      <c r="L19" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="M17" s="2" t="s">
+      <c r="M19" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="B18" s="4"/>
-      <c r="I18" s="2">
+    <row r="20" spans="1:13" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="B20" s="4"/>
+      <c r="I20" s="2">
         <v>1</v>
       </c>
-      <c r="J18" s="13" t="s">
+      <c r="J20" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="K18" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L18" s="2">
-        <v>1800</v>
-      </c>
-      <c r="M18" s="2"/>
-    </row>
-    <row r="19" spans="1:13" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="C19" s="27">
-        <v>135</v>
-      </c>
-      <c r="I19" s="2">
-        <v>2</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L19" s="2">
-        <v>1800</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="15" x14ac:dyDescent="0.3">
-      <c r="A20" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="C20" s="27">
-        <v>136</v>
-      </c>
-      <c r="E20" s="14"/>
-      <c r="I20" s="2">
-        <v>3</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>43</v>
+      <c r="K20" s="13" t="s">
+        <v>54</v>
       </c>
       <c r="L20" s="2">
         <v>1800</v>
       </c>
       <c r="M20" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" s="27">
+        <v>135</v>
+      </c>
+      <c r="I21" s="2">
+        <v>2</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L21" s="2">
+        <v>1800</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="15" x14ac:dyDescent="0.3">
+      <c r="A22" s="25" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" ht="15" x14ac:dyDescent="0.3">
-      <c r="A21" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="B21" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="C21" s="27">
+      <c r="B22" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" s="27">
+        <v>136</v>
+      </c>
+      <c r="E22" s="14"/>
+      <c r="I22" s="2">
+        <v>3</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L22" s="2">
+        <v>1800</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="15" x14ac:dyDescent="0.3">
+      <c r="A23" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="27">
         <v>137</v>
       </c>
-      <c r="E21" s="15"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="I21" s="2">
-        <v>4</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="L21" s="2">
-        <v>3300</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="26"/>
-      <c r="B22" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="C22" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="I22" s="2">
-        <v>5</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="K22" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="L22" s="3">
-        <v>4200</v>
-      </c>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="1:13" ht="15.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="26"/>
-      <c r="B23" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="C23" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="E23" s="17"/>
+      <c r="E23" s="15"/>
       <c r="F23" s="18"/>
       <c r="G23" s="18"/>
       <c r="I23" s="2">
-        <v>6</v>
-      </c>
-      <c r="J23" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="K23" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="L23" s="3">
-        <v>4800</v>
-      </c>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="1:13" ht="15.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="26" t="s">
-        <v>117</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L23" s="2">
+        <v>3300</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="26"/>
       <c r="B24" s="26" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>62</v>
-      </c>
-      <c r="E24" s="17"/>
+        <v>56</v>
+      </c>
       <c r="F24" s="18"/>
       <c r="G24" s="18"/>
       <c r="I24" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="K24" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="K24" s="13" t="s">
         <v>55</v>
       </c>
       <c r="L24" s="3">
-        <v>4800</v>
-      </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="1:13" ht="15.5" x14ac:dyDescent="0.3">
+        <v>4200</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="15.5" x14ac:dyDescent="0.25">
       <c r="A25" s="26"/>
       <c r="B25" s="26" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E25" s="17"/>
       <c r="F25" s="18"/>
       <c r="G25" s="18"/>
       <c r="I25" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J25" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="K25" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="L25" s="3">
+        <v>4800</v>
+      </c>
+      <c r="M25" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="K25" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="L25" s="29">
-        <v>6000</v>
-      </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="1:13" ht="14" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:13" ht="15.5" x14ac:dyDescent="0.25">
       <c r="A26" s="26" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B26" s="26" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C26" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="E26" s="20"/>
+        <v>61</v>
+      </c>
+      <c r="E26" s="17"/>
       <c r="F26" s="18"/>
       <c r="G26" s="18"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
+      <c r="I26" s="2">
+        <v>7</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="K26" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="L26" s="3">
-        <f>SUM(L18:L25)</f>
-        <v>28500</v>
-      </c>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="1:13" ht="14" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="26" t="s">
-        <v>116</v>
-      </c>
+        <v>4800</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="15.5" x14ac:dyDescent="0.3">
+      <c r="A27" s="26"/>
       <c r="B27" s="26" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="E27" s="21"/>
-      <c r="F27" s="22"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="1:13" ht="12.5" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+      <c r="E27" s="17"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+      <c r="I27" s="2">
+        <v>8</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L27" s="29">
+        <v>6000</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="14" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="26" t="s">
-        <v>67</v>
+        <v>117</v>
       </c>
       <c r="B28" s="26" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C28" s="27" t="s">
-        <v>64</v>
-      </c>
-      <c r="E28" s="23"/>
-      <c r="F28" s="24"/>
+        <v>59</v>
+      </c>
+      <c r="E28" s="20"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
       <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="1:13" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="J28" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="L28" s="58">
+        <v>6000</v>
+      </c>
+      <c r="M28" s="59" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="14" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="26" t="s">
-        <v>68</v>
+        <v>115</v>
       </c>
       <c r="B29" s="26" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C29" s="27" t="s">
-        <v>71</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="E29" s="21"/>
+      <c r="F29" s="22"/>
       <c r="I29" s="3"/>
-      <c r="J29" s="3"/>
+      <c r="J29" s="2"/>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
     </row>
-    <row r="30" spans="1:13" ht="15.5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A30" s="26" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B30" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="C30" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="C30" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="19"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="24"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
     </row>
-    <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A31" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="C31" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="B31" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="C31" s="27" t="s">
-        <v>66</v>
-      </c>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
-    </row>
-    <row r="32" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="28" t="s">
-        <v>80</v>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="1:13" ht="15.5" x14ac:dyDescent="0.25">
+      <c r="A32" s="26" t="s">
+        <v>68</v>
       </c>
       <c r="B32" s="26" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C32" s="27" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="E32" s="17"/>
       <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
+      <c r="G32" s="19"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
     </row>
     <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="28" t="s">
-        <v>41</v>
+      <c r="A33" s="26" t="s">
+        <v>69</v>
       </c>
       <c r="B33" s="26" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C33" s="27" t="s">
-        <v>76</v>
-      </c>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
+        <v>65</v>
+      </c>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
     </row>
     <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="28" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B34" s="26" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C34" s="27" t="s">
-        <v>77</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
     </row>
     <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="28" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C35" s="27" t="s">
-        <v>78</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
     </row>
     <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="28" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B36" s="26" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C36" s="27" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="26"/>
+      <c r="A37" s="28" t="s">
+        <v>72</v>
+      </c>
       <c r="B37" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="C37" s="27"/>
+        <v>62</v>
+      </c>
+      <c r="C37" s="27" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="16"/>
+      <c r="A38" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="B38" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="C38" s="27" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="16"/>
+      <c r="A39" s="26"/>
+      <c r="B39" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="27"/>
     </row>
     <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C40" s="16"/>
@@ -1792,6 +1990,12 @@
     </row>
     <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C43" s="16"/>
+    </row>
+    <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C44" s="16"/>
+    </row>
+    <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C45" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
@@ -1813,24 +2017,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" t="s">
         <v>82</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>83</v>
-      </c>
-      <c r="C1" t="s">
-        <v>84</v>
       </c>
       <c r="D1" t="s">
         <v>9</v>
       </c>
       <c r="E1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B2" s="7">
         <v>29344</v>
@@ -1841,7 +2045,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B3" s="7">
         <v>33599</v>
@@ -1852,7 +2056,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B4" s="7">
         <v>37332</v>
@@ -1863,7 +2067,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B5" s="7">
         <v>45980</v>
@@ -1874,7 +2078,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B6" s="7">
         <v>48923</v>
@@ -1885,7 +2089,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B7" s="8">
         <v>33599</v>
@@ -1896,7 +2100,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B8" s="8">
         <v>46881</v>
@@ -1907,7 +2111,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B9" s="8">
         <v>43678</v>
@@ -1953,7 +2157,7 @@
   <sheetData>
     <row r="1" spans="1:10" s="30" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="32" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B1" s="36" t="s">
         <v>6</v>
@@ -1962,22 +2166,22 @@
         <v>4</v>
       </c>
       <c r="D1" s="36" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F1" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1" s="36" t="s">
         <v>82</v>
       </c>
-      <c r="G1" s="36" t="s">
+      <c r="H1" s="36" t="s">
         <v>83</v>
       </c>
-      <c r="H1" s="36" t="s">
-        <v>84</v>
-      </c>
       <c r="I1" s="32" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J1" s="32" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -1985,16 +2189,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C2" s="40">
         <v>29344</v>
       </c>
       <c r="D2" s="37" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F2" s="38" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G2" s="43">
         <v>29344</v>
@@ -2010,16 +2214,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="37" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C3" s="40">
         <v>43238</v>
       </c>
       <c r="D3" s="37" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F3" s="38" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G3" s="43">
         <v>33599</v>
@@ -2035,16 +2239,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="37" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C4" s="40">
         <v>20000</v>
       </c>
       <c r="D4" s="37" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F4" s="38" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G4" s="43">
         <v>37332</v>
@@ -2060,16 +2264,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C5" s="40">
         <v>29149</v>
       </c>
       <c r="D5" s="37" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F5" s="38" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G5" s="43">
         <v>45980</v>
@@ -2085,16 +2289,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="37" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C6" s="40">
         <v>30000</v>
       </c>
       <c r="D6" s="37" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F6" s="38" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G6" s="43">
         <v>48923</v>
@@ -2110,16 +2314,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="37" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C7" s="40">
         <v>50000</v>
       </c>
       <c r="D7" s="37" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F7" s="38" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G7" s="43">
         <v>33599</v>
@@ -2135,16 +2339,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="37" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C8" s="40">
         <v>75219</v>
       </c>
       <c r="D8" s="37" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F8" s="38" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G8" s="43">
         <v>46881</v>
@@ -2158,7 +2362,7 @@
     <row r="9" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="9"/>
       <c r="B9" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C9" s="41">
         <f>SUM(C2:C8)</f>
@@ -2166,7 +2370,7 @@
       </c>
       <c r="D9" s="38"/>
       <c r="F9" s="38" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G9" s="43">
         <v>43678</v>
@@ -2181,7 +2385,7 @@
       <c r="A10" s="46"/>
       <c r="D10" s="47"/>
       <c r="F10" s="37" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G10" s="9"/>
       <c r="H10" s="44">
@@ -2193,7 +2397,7 @@
     <row r="11" spans="1:10" ht="13" x14ac:dyDescent="0.3">
       <c r="A11" s="48"/>
       <c r="F11" s="36" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G11" s="36">
         <f>SUM(G2:G9)</f>
@@ -2213,13 +2417,13 @@
     <row r="12" spans="1:10" ht="13" x14ac:dyDescent="0.3">
       <c r="A12" s="48"/>
       <c r="B12" s="32" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C12" s="35">
         <v>319336</v>
       </c>
       <c r="D12" s="33" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F12" s="38"/>
       <c r="G12" s="38"/>
@@ -2230,13 +2434,13 @@
     <row r="13" spans="1:10" ht="13" x14ac:dyDescent="0.3">
       <c r="A13" s="48"/>
       <c r="B13" s="32" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C13" s="35">
         <v>28500</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F13" s="38"/>
       <c r="G13" s="38"/>
@@ -2247,10 +2451,10 @@
     <row r="14" spans="1:10" ht="13" x14ac:dyDescent="0.3">
       <c r="A14" s="48"/>
       <c r="B14" s="32" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D14" s="9"/>
       <c r="F14" s="38"/>
@@ -2262,10 +2466,10 @@
     <row r="15" spans="1:10" ht="13" x14ac:dyDescent="0.3">
       <c r="A15" s="48"/>
       <c r="B15" s="32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C15" s="34" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D15" s="9"/>
       <c r="F15" s="38"/>
@@ -2288,7 +2492,7 @@
     <row r="17" spans="1:10" ht="13" x14ac:dyDescent="0.3">
       <c r="A17" s="48"/>
       <c r="B17" s="32" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C17" s="51">
         <v>70886</v>
